--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7140,6 +7140,33 @@
       <c r="E158" t="inlineStr">
         <is>
           <t>Claude (self-corrected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>August 14th Design — one folder for the live set, and all 32 decisions re-verified against the files</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Founder: create a folder called August 14th Design, move the latest files there so there is no confusion, and re-check every file carries the decisions we made. DONE, BOTH HALVES. The folder now holds the Plan brief (renamed to 2026-08-14 because its old name said the 12th while it had been revised materially today), the Home brief, the handoff review, Claude Design's own delivered files, and a README stating which file is live and what is deliberately absent. Superseded work stays where it is — brief v1 and v2 and the 08-12 review in mockups/Plan-redesign-Aug-12/, three older Claude Design copies in A-instructions for claude/ — because the mock-first rule keeps old versions but does not keep them where they can be mistaken for current. Every reference to a moved file was repointed and checked. THE RE-CHECK WAS RUN AGAINST THE FILES, NOT FROM MEMORY: 32 decisions from this engagement were each tested for by searching the document or the source that should carry them. 31 passed on the first pass. ONE FAILED — the hide-balances ruling was described accurately in the Plan brief but did not quote the founder's own five words, 'hide the number, keep the shape', so a reader could not tell a ruling from my paraphrase of one. Now quoted identically in both briefs. Coverage: 32 of 32.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>The founder asked for confusion removed and the decisions verified; a check run from memory would have proved nothing.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7165,6 +7165,33 @@
         </is>
       </c>
       <c r="E159" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>The word "safe" is swept out of everything the user can read — and a gate now stops it returning</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Founder: do it as one sweep. DONE — 34 user-visible replacements across 16 files, using the wording already approved in brief v3 §7.1: Safe to spend → LEFT TO SPEND (the retiree hero on Home, the Cash flow heading, the month-detail heading and total, the 12 paycheck months and every spoken label behind them); Safe draw from savings → Draw from savings (the paycheck card, Plan hub, Cash flow, month detail, paycheck months, and the glossary entry every information dot on that line reads from); a safe pace → within the ~4% guideline; Your safety net → Your cushion (the job-safety screen heading and the reward badge); 'the safer basis' → 'the steadier basis' on the returns warning; and the first-run promise now says what's left to spend. OUT OF SCOPE ON PURPOSE, as the brief states: uses with nothing to do with money — 'your data is safe' after a failed import, 'I've saved my recovery code somewhere safe', the job-safety feature name, and internal code identifiers nobody reads. THE GUARD IS THE POINT, NOT THE SWEEP. A sweep only fixes today; src/__tests__/banned_word_guard.test.ts fails the build if the word reappears in any rendered string, label, title or spoken label in screens, components or domain. IT EARNED ITSELF IMMEDIATELY: it caught a visible section heading in month detail that still read SAFE TO SPEND, which my hand-sweep had walked straight past — a live demonstration that reading carefully is not a substitute for a gate. Suite 1665 green, typecheck clean, quality gate passing.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Standing rule since 2026-08-12: we never call money safe, because we do not know and will not say anything binding.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7192,6 +7192,33 @@
         </is>
       </c>
       <c r="E160" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Plan · spend-more — the odds beside the control must be LIVE; $5,600 must say what it is</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Founder read June's spend-more row and asked what the $5,600 meant. Two defects in one line, both now written into brief §3.5 and logged as blocker B7 in the handoff review. FIRST, THE ODDS ARE WRONG AT THE DEFAULT AND CONTRADICT THE SAME SCREEN. The phrase 'held at odds of 80%' explains how the $2,555 was CALCULATED — the largest extra draw that still holds an 80% floor — and the brief attaches it to that figure. The handoff moved it onto the running total, where it is false everywhere except the far end. Measured on the engine: at $0 extra June is at 100%, still 100% at $500 and $1,000 extra, then 97% at $1,500, 90% at $2,000, and 80% only at the $2,555 maximum. As drawn, the screen would print 80% directly beneath a dial reading 100% for the identical plan — that reads as a broken app, not a nuance. The odds beside a live control must themselves be live, which is brief §6.1 (odds are only ever an output) applied to a stepper. The real curve is also a better answer than the static one: her first $1,000 a month costs her nothing, which is exactly what she came to that row to find out. SECOND, $5,600 IS UNLABELLED. At zero extra it is simply what she spends today, but an arrow pointing at it reads as the result of a decision she has not made; it needs naming at rest and becomes a '→ … in total' only once the control moves. The brief also now requires one sentence linking draw and spend — her guaranteed $4,000 does not change, so every extra dollar spent is an extra dollar drawn. Whole curve pinned in src/__tests__/june_numbers_probe.test.ts so the build cannot reintroduce a static odds figure. Nothing to build today: this control is the redesign, not shipped code.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Founder-found 2026-08-14 reading the design; a wrong number beside a live control is the worst place for one.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7221,6 +7221,33 @@
       <c r="E161" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Plan · "Can I spend more?" — plain-English rewrite MOCKED, awaiting founder approval</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Founder: too complex for someone with no finance background; put it in simple terms. MOCKED, NOT BUILT, per the mock-first rule — mockups/Plan-redesign-Aug-12/spend-more-plain-english-v1-2026-08-14.html, three full phone frames (as-drawn, plain at rest, plain pushed to the maximum) with every number taken from the engine and pinned by june_numbers_probe. THE DIAGNOSIS: the row made her work out four things unaided — what 'draw' means and how it differs from spend, why $2,555 is offered while $0 shows, what $5,600 is (it is what she already spends, and nothing said so), and what 'odds of 80%' refers to when the dial above reads 100%. THE REWRITE: the answer comes first and it is the free money — 'Yes, about $1,000 a month more, and nothing changes', because the engine's own curve holds 100% all the way to $1,000 extra. That was the single most useful fact on the row and the static 80% label was hiding it. Consequence is then stated as counts rather than percentages — 'your money lasts in about 4 futures out of 5, in the other 1 it runs out before 94' — because counts land with people who bounce off percentages, and the sentence names what happens in the losing case instead of leaving her to imagine it. One line closes the draw-versus-spend gap: 'Your Social Security and pension don't change, so anything extra comes out of savings.' WORDS REMOVED FROM THE ROW: draw, odds, held at, floor. WORDS KEPT: spend, month, lasts, runs out. NEEDS A FOUNDER CALL BEFORE IT GOES IN THE BRIEF: 'estimated amount you can draw more every month' is the founder's own wording and brief v3 §3.5 currently says it must not be softened or shortened. The mock removes it. That instruction is his to withdraw, not mine — the brief is unchanged until he says so.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14: 'It is too complex for user to understand particularly someone with no finance background.'</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWAITING founder approval</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7248,6 +7248,33 @@
       <c r="E162" t="inlineStr">
         <is>
           <t>AWAITING founder approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Plan · "Can I spend more?" — plain-English rewrite APPROVED, and the count rule now binds every decision row</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Founder: 'like B and C.' The plain-English frames are approved and are now brief §3.5 verbatim. The row leads with the answer — 'Yes, about $1,000 a month more, and nothing changes' — because the engine holds 100% all the way to $1,000 extra and that free headroom was the most useful fact on the row, buried under a static 80% label. Consequence is stated as a count with the losing case named: 'lasts in about 4 futures out of 5, in the other 1 it runs out before 94.' One sentence closes the draw-versus-spend gap. Words removed: draw, odds, held at, floor. THE FOUNDER'S OWN LINE IS WITHDRAWN BY THIS APPROVAL: 'estimated amount you can draw more every month' was his wording and the brief previously forbade softening it; frames B and C do not contain it, so approving them withdraws that instruction. Recorded explicitly rather than assumed, and reversible on a word from him. THE RULE GENERALISED RATHER THAN STOPPING AT ONE ROW (§3.5.1): wherever a decision row says what a choice does to the chance a plan works, it says it as a count out of a round number, never a percentage, and names what happens in the losing case. Applied on the spot to the MORTGAGE row, which ended 'your odds go from 48% to 43%' and now reads 'your money lasts in about 5 futures out of 10 today, and about 4 out of 10 if you do this' — same facts, and it finally says which way is worse. The Social Security row already passes and is named as the benchmark. One word left for the designer: 'pre-tax' on the Roth row, flagged with a suggested replacement rather than left alone.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 approving frames B and C of the plain-English mock; the audience is 55-70 with no assumed finance background.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7273,6 +7273,60 @@
         </is>
       </c>
       <c r="E163" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Plan · Retire — "Pay off the mortgage early" MOVES to Cash flow · Debt</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Founder: 'let's move Pay off the mortgage early to Cash flow · Debt. It does not belong under Retire.' Done in brief §3.3.1 — same control, drawn in a different place. It only ever sat on Retire because its side-effect lands on retirement, which is a reason to carry the consequence, not a reason to put a debt decision on a retirement screen; a person thinking about their mortgage goes looking for their mortgage. THE RISK OF THIS CHANGE IS NAMED IN THE BRIEF AS THE MAIN INSTRUCTION: the retirement consequence must travel with the control. Paying a mortgage down faster is money not going into savings, and that is the single most important thing to know before doing it — if the control moves to Debt and the effect stays behind on Retire, the person decides blind to its biggest consequence, which is worse than where we started. The line moves too, in the approved count grammar: 'your money lasts in about 5 futures out of 10 today, and about 4 out of 10 if you do this.' KNOCK-ON FLAGGED RATHER THAN PAPERED OVER: this leaves Pat with ONE decision row, since at 58 the Social Security row does not reach him for two years. The brief instructs the designer to draw that one-row state and NOT to invent a third row to balance the block — at 58 with a mortgage and a plan on track there genuinely is little to decide this month, and that emptiness is real information. Two things left for the designer to choose and state: whether Debt shows the control on the mortgage row or beneath the debt list, and whether Retire keeps a quiet pointer to it (my view: it earns its place, since someone reading their odds has no other way to learn the biggest lever is on another tab).</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; a debt decision belongs where the debt is.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Ray — the line under his dial was too harsh, AND it was wrong in the reassuring direction</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Founder: 'It is too harsh.' He was reading "He'll likely never close that $250,000 by saving $500/mo — and his odds are fine anyway" as screen text. He was right twice. FIRST, HARSH: telling a 64-year-old he will never reach his retirement target is a projection dressed as a prophecy, and nobody should read that sentence about their own money on a Tuesday morning. SECOND, AND I MISSED THIS UNTIL HIS NOTE SENT ME BACK TO IT: the reassuring half was false. Ray sits at 73%, and the app holds an 80% line everywhere — so 'his odds are fine anyway' was not a kind framing of a hard truth, it was simply untrue. The passage managed to be both unnecessarily bleak and quietly inaccurate in the same breath. REWRITTEN. The brief now marks that whole passage as ANALYSIS FOR THE DESIGNER, NOT COPY, because it was ambiguous enough that the founder read it as screen text — which means a designer could have set it. What Ray actually sees is a statement of position followed by a door: '$500,000 of the $750,000 you set — short $250,000. Your money lasts in about 7 futures out of 10. Waiting to claim Social Security at 70 takes that to about 8 in 10 — the biggest single change available to you.' The gap stays visible, the number below the line is not softened, and the fix is one row away. THREE RULES ADDED FOR ANYONE SHORT OF THEIR TARGET, not just Ray: never tell someone they will not get there; never soften a number that is below the line; never state a shortfall without the nearest thing they can do about it — a gap on its own is an accusation, a gap with a door beside it is a plan.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and the check found the sentence was inaccurate as well as unkind.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7327,6 +7327,60 @@
         </is>
       </c>
       <c r="E165" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BUG (live, silent) — the ten-year Treasury feed was dead and serving a fallback as if it were live</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Found while specifying the founder's mortgage-versus-Treasury comparison, which depends on this number being real. The app fetched the yield from the Treasury Fiscal Data 'average interest rates' dataset. THAT ENDPOINT NOW RETURNS 404 FOR EVERY REQUEST — the whole dataset, not just our filter — so the live fetch had been failing silently and the app served the 4.35% fallback while the actual ten-year sat at 4.63%. Nobody noticed because falling back is a legitimate outcome of that code path; it fails quietly by design. IT WAS ALSO THE WRONG NUMBER WHEN IT WORKED: 'average interest rate on marketable Treasury Bonds' is the weighted average coupon across all outstanding long bonds, a slow-moving historical figure — not the ten-year yield, which is what the market pays today and the only version of the number that means anything in a mortgage decision. The field was named treasuryYield and commented '10-year yield %' throughout. FIXED: now reads the Federal Reserve's own DGS10 daily ten-year constant-maturity series through FRED's CSV endpoint, which needs no key. The parser walks backwards past closed-market days (FRED writes those as a lone '.') so a weekend never becomes the yield, and rejects any reading outside 0-25% as a changed feed rather than a moved market — falling back and FLAGGING rather than putting nonsense on a screen someone is about to make a six-figure decision on. Four tests pin it, including one that fails if the dead endpoint ever returns to the source.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>The mortgage comparison the founder asked for is only as good as this number.</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Claude (found while building the founder request)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Plan · Debt — the mortgage decision now compares the mortgage rate against the ten-year Treasury</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Founder: 'one critical factor is whether the current mortgage rate is higher or lower than the return on investment or the 10-year yield — if a person pays off the mortgage versus keeping money in a 10-year Treasury, what would be the net saving or cost?' Written into brief §3.3.1. WHY THE TREASURY IS THE RIGHT COMPARATOR, AND THE BRIEF SAYS SO: paying a mortgage down is a GUARANTEED return equal to the mortgage rate, so the fair comparison is against another guaranteed thing. Comparing it to shares weighs a certainty against a hope, which is how people talk themselves into the wrong answer — the brief keeps one sentence acknowledging shares might earn more, and says plainly that only one of the two is certain. PAT'S NUMBERS, COMPUTED AND RECONCILING: mortgage 5.50%, ten-year 4.63%, a gap of 0.87 points worth about $3,584 a year at his balance. Over a common horizon with identical monthly outlay of $2,900, putting $500/mo into Treasuries reaches $346,678, while paying the mortgage down and then investing everything it frees reaches $383,255 — paying down leaves him $36,577 ahead. The independent model also reproduced the brief's existing $143,300 interest saving to the dollar, so the old figures and the new ones agree. THREE GUARDS ON IT. Never tell them what to do — state both rates and the dollar difference, and stop. Never hide it when the answer flips: anyone holding a 2021 loan at 3% is BELOW the yield and the same sentence must say paying down COSTS them, drawn as a required state, because a comparison that only ever supports paying down is not a comparison. And never quietly do the tax — Treasury interest is federally taxable and mortgage interest is only deductible for someone who itemises, which most of this audience no longer does; both push the same way, so the note is directional and no per-person number is printed.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; it is the question the decision actually turns on and the screen never asked it.</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7381,6 +7381,60 @@
         </is>
       </c>
       <c r="E167" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Plan · Debt — the exact mortgage-versus-Treasury wording, in BOTH directions</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Founder asked what the text will say exactly. Written verbatim into brief §3.3.1, same sentence shape either way so nobody can tell from the layout which answer they are getting. ABOVE THE YIELD (Pat, 5.5% against 4.63%): 'Your mortgage costs 5.5%. A ten-year Treasury pays 4.63% today. So a dollar into your mortgage saves you more than the same dollar would earn sitting in Treasuries — about $3,584 a year at your balance. Over the life of the loan, paying the extra $500 a month leaves you around $36,577 better off than putting it in Treasuries instead. Shares might earn more than either — or less. Paying the mortgage is the only one that is certain.' BELOW THE YIELD (a 2021 loan at 3.1%): identical shape, 'saves you less', about $6,304 a year, and around $40,217 WORSE OFF. THE SECOND NUMBER IS BIGGER THAN THE FIRST, and that is the point of the feature: someone holding a cheap 2021 loan loses more by paying it down early than Pat gains by paying his down — against 'pay off your mortgage', the most repeated advice this audience has ever been given. The brief says plainly that drawing only the first frame ships something that agrees with received wisdom and stays quiet when it is wrong. A THIRD STATE ADDED: within about a quarter-point, say neither is clearly better rather than picking a winner — a dollar figure implying precision we do not have is worse than none.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 asked for the exact words; both directions matter more than either alone.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Plan · day one — a button naming no question, and four of the seven glance rows missing</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Two founder findings on the first screen a person ever sees, both confirmed against the handoff and both now brief §5 state 4 and review blocker B8. (a) The top button reads 'Answer the first question' and does not say which — a button you must press to find out what it does, on day one. It becomes 'Add your age'. The frame immediately before it already does this correctly, and the SHIPPED APP is ahead of the mock here because it names the specific missing item, so as drawn this is a step backwards from live behaviour. (b) The glance shows three questions on day one and seven everywhere else; the founder asked where plan-to-age and target nest egg went. THE DECIDING ARGUMENT IS NOT CONSISTENCY, IT IS HONESTY: four of the missing rows are not blank, they are OURS. With nothing answered the app still assumes retire at 65, plan to 90, a 6% return and 2.5% inflation — and the sample gauge on that same frame is computed with them. Hiding those rows hides the assumptions the number on screen is standing on, which is precisely what §7.2 forbids. Fix: all seven rows always, unanswered ones saying Add, assumed ones showing the value with a quiet 'ours until you change it'. The person then sees the whole shape of what they are being asked AND which parts we filled in for them.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and the assumption-hiding is a rule breach, not just an inconsistency.</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7435,6 +7435,60 @@
         </is>
       </c>
       <c r="E169" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Plan — the two hardest states rewritten in plain English, and TWO ERRORS in the brief found doing it</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Founder: 'this is assuming the user knows what these odds mean and how to use it — which is not the case 99% of the time.' Brief §5 state 6 and its mirror rewritten to that instruction. WHAT THE ODDS ARE IS NOW SAID ON THE SCREEN, not left to a glossary: 'We play out your retirement 400 times with different market luck. This counts how many of them your money lasted through.' It appears under the number, always — this is precisely where a person meets a percentage that contradicts something else they can see, and without knowing what it counts they cannot resolve it. Both states now read as plain sentences with counts rather than percentages. TWO ERRORS FOUND WHILE REWRITING, BOTH IN THE PASSAGE ITSELF. FIRST: the state said Pat's odds were 45%. That is his ASSETS-VERSUS-TARGET figure against a $2,000,000 target — the other dial. Typing a different target cannot move the odds by a point, so his odds are 48% here as everywhere. On the one state whose entire purpose is stopping two numbers being confused, the brief confused them. SECOND: it instructed the designer to write that 'saving is no longer the lever'. Measured on the engine, Pat saving nothing sits at 45%, at $24,000 a year 64%, at $84,500 a year 90% — saving is an enormous lever. What is true is narrower: he is past his TARGET, so the 'save this much to reach your number' sentence has nothing left to close. That is a sentence losing its job, not a lever disappearing, and telling someone their savings no longer matter would have been false and discouraging at once. The mirror case was verified and holds exactly: a $1,500,000 target is reached by saving $24,000 a year, projecting $1,506,263, with odds of 64%.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and the rewrite surfaced a wrong number and a false instruction.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Plan — Goals and Prepare need landing screens; the brief had told the designer not to draw them</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Founder: 'no design created for Goals and Prepare tabs.' Correct, and OUR instruction caused it — §3.0 said Retire was 'the only one being redesigned in this pass'. That was the wrong thing to write: a three-tab bar where two tabs open onto nothing designed is not a finished design, and a person tapping Prepare on day one has to land somewhere deliberate. Brief §3.0.1 now specifies both landing views and the deliverables list asks for each in a populated AND an empty state. GOALS: the goals themselves with target, progress and on-track state; 'Can I afford it all?' promoted to the front door because with more than one goal that is the real question; the college planner — and the empty state matters more here than anywhere, since most people arrive with no goals set. PREPARE: insurance, estate, tax organiser, build credit, stress test, job safety — mostly things done once, so the useful state is 'not started' or 'done, March 2026' rather than a number; a row saying just 'Estate' tells nobody anything. Both are lopsided against Retire on purpose and the brief says not to pad them for symmetry. SCOPE STATED HONESTLY RATHER THAN ABSORBED: this is a real expansion of the ask, and the designer is told to say so if it does not fit this pass so we can split it, rather than returning one tab drawn and two empty. Logged as blocker B9 — nine now, four of them found by the founder reading the design rather than by my audit.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; two undesigned tabs cannot ship behind a tab bar that offers them.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7489,6 +7489,33 @@
         </is>
       </c>
       <c r="E171" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PROCESS — briefs are now verified by a test, after the founder asked how to stop errors shipping as instructions</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Founder: 'how to avoid this in the next brief?' The honest answer is that more care would not have helped — all three errors were written while reading carefully, and two survived several review passes because they looked plausible. A brief is a document full of claims the code can settle, and nothing was settling them. BUILT: src/__tests__/brief_figures_guard.test.ts recomputes every persona figure from the engine and fails the build when the brief and the engine disagree — Pat's $84,500 and where it lands, state 6 and its mirror at $1,506,263 and 64%, June's $4,155 draw and the live spend-more curve at 100% and 80%, Ray's $3,224 and the 73-to-80 move, and the mortgage comparison in both directions. It also asserts the deleted false claim stays deleted. IT CAUGHT TWO THINGS ON ITS FIRST RUN, one a real bug in the test (solveSafeDraw silently returns NaN without the ages) and one a rule too blunt to keep (banning '4.35%' outright failed on the note explaining the dead feed). AND IT SURFACED SOMETHING BIGGER THAN THE THREE ERRORS: PAT'S 48% IS NOT REPRODUCIBLE FROM PAT'S OWN NUMBERS. His four accounts blend to an 8.65% return by the app's own calculation, which puts him at 82% — the 48% only appears at a 5.5% return that appears NOWHERE in the brief. He is the persona the brief opens with and every state is built on him. Recorded in his table as a founder decision with three options (change his holdings, accept 82%, or write down the return we intend) and explicitly NOT resolved by me. The shapes in the brief are unaffected either way, since they concern how the screen behaves rather than which value it holds. FOUR RULES ADDED TO CLAUDE.md: every brief number is engine-computed or labelled founder-stated; any causal claim is measured before it is written; any claim about current behaviour is checked against shipped code, not memory; and a figure with no recorded provenance is a defect even when nobody can prove it wrong. Three guards now exist — orphan routes, the banned word, brief figures — and each caught a real defect within minutes of being written, on surfaces already read carefully by hand.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; careful reading finds some, a gate finds the rest.</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7518,6 +7518,33 @@
       <c r="E172" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Pat's numbers now follow from Pat's holdings — and I stopped asking the founder to adjudicate my own error</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Founder: 'not sure what you want me to check here.' He was right and the framing was mine. I presented three options as a product decision when it was a technical correction: the brief is built end to end around Pat being someone whose plan needs work, so the story was never in question — only the numbers were. FIXED RATHER THAN ESCALATED. Pat's holdings changed, his story did not, and his total stayed at $909,152 so every other figure in the brief still reconciles. He now holds a $380,000 IRA, $379,152 in plain savings, $90,000 in a brokerage and a $60,000 Roth — which the app's own calculation blends to 5.85%, giving him 67% odds. THE NEW MIX IS ALSO THE BETTER TEACHING CASE: 42% of his retirement money sits in a savings account earning about 2.4%, which is extremely common at this age and something the app already has an insight for. His problem is now visible in his own account list instead of hiding inside an unstated assumption. A SECOND MISSING INPUT SURFACED WHILE FIXING THE FIRST: the brief had never said what Pat currently saves, and the mortgage row redirects money FROM saving — so that row could not be computed by anyone reading the brief. It is now $12,000 a year, stated in his table alongside the expected growth, which was also missing. EVERYTHING DOWNSTREAM WAS RECOMPUTED FROM THE ENGINE, NOT ADJUSTED BY HAND: the closing sentence is now $77,500 landing at $2,008,196 with one step lower missing at $1,989,909; the growth breakdown is $426,859 on what he has, $542,500 put in, $129,685 on the new money; state 6 reads 1 future in 3; the mirror is $17,500 reaching $1,505,001 at 74%, so on-target-but-short-of-the-line still holds; the mortgage line is 67 out of 100 to 65 out of 100. Nine guard tests pin all of it. The guard also caught two of my own mistakes today — a probe that silently read default returns because I spread the wrong field names, and two assertions too blunt to tell history from a live figure.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and I should have fixed it rather than handing him three options.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Claude (self-corrected after founder pushback)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7545,6 +7545,33 @@
       <c r="E173" t="inlineStr">
         <is>
           <t>Claude (self-corrected after founder pushback)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Plan — the hero never carries a door the decisions list already opens (Ray's 'see what waiting is worth')</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Founder: 'Ray 64 — see what waiting is worth? Where does that take you, as when should I claim Social Security is below on the same screen.' The question exposed the defect: the link and the Social Security row sat a few centimetres apart on one screen — two doors to one place, one above the other, on a surface we have already been told is too busy. And a link that scrolls a short way down the same page is the worst option of all: this audience taps it expecting a new screen and gets what looks like nothing happening. FIXED. The hero now names the lever and says where it is — 'the biggest single thing you could change is when you claim Social Security, it is the first decision below' — with no link. That still honours the rule that a shortfall is never stated without the nearest thing they can do about it: the fix is named AND located, just not linked twice. THE DIVISION OF LABOUR IS NOW STATED AS THE PATTERN FOR THE WHOLE SCREEN: the hero gives a decision's effect on the ODDS (7 in 10 to 8 in 10), the row gives it in DOLLARS ($624 a month). Two useful facts about one decision, each where it belongs — not one sentence printed twice. GENERALISED: the hero never carries a door to something the decisions list already opens; if a hero sentence wants a link, that is a sign the decision belongs in the list and is missing from it. AND IT SETTLED AN OPEN QUESTION ELSEWHERE: §3.4 had been leaving it to the designer whether the dated 'next decision' card should exist or become the first row of the decisions list. The same principle decides it — recommendation is to drop the separate card. That one IS flagged for the founder rather than decided, because the card is built and shipping and a test pins it, so removing it changes something already approved.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; two doors to one place on one screen, a few rows apart.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7570,6 +7570,60 @@
         </is>
       </c>
       <c r="E174" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Wording — "target nest egg" everywhere, and counts are "future simulations" not "futures"</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Two founder naming rules, both now binding on the whole surface and both in brief §3.5.1. CALL IT THE TARGET NEST EGG: not 'the number you set', not 'your target', not 'your number'. Ray's hero now reads '$500,000 of your $750,000 target nest egg', and the same correction applied to both hard states. The app already uses that exact label in the one place it appears, and it is the wording of the question in §3.2, so the screens agree. COUNT IN FUTURE SIMULATIONS: '7 future simulations out of 10', never '7 futures out of 10'. On its own the word 'futures' reads as though we are making predictions about someone's life; 'future simulations' says plainly that these are runs of a model, which is the entire point of the sentence. Applied to every count in the brief and pinned by the figures guard, which now fails if the bare form returns. A LIVE GAP FOUND WHILE CHECKING THE FIRST RULE AND FLAGGED RATHER THAN FIXED: the shipped app has NO typed target at all. Its 'Target nest egg' row shows a figure WE derive — the pot that would reach 80% odds — so the label is right but the number is ours, not theirs. That is exactly what the founder corrected at the start of this engagement ('target nest egg is a number entered by user'). The redesign introduces the typed value; noting it so the gap is not mistaken for done.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; the words have to say what the number actually is.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Plan — the dated "next decision" card is REMOVED; the obligation leads the decisions list wearing its date</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Founder: 'good with your recommendation.' BUILT, not just briefed, because the card was shipping. The amber card used to sit above the decisions list while the list below deliberately OMITTED whatever the card was showing — so one decision occupied two positions on one screen, and the list quietly changed shape depending on what happened to be due. Same defect as the link in Ray's hero, in a different jacket: one decision, one place. Now the dated obligation is simply the FIRST row of the list, wearing 'DUE DEC 31' in amber above its title. That is also where the ordering rule already wanted it — §3.3 says anything with a real deadline goes first because it expires — so this is not a compromise, it is that rule being followed properly for the first time. The exclusions that existed only to stop the card and the list duplicating each other are gone with it, which removes a whole class of shape-shifting from the list. DecisionRow gained an optional date, the accessibility label carries it, and two tests pin the new behaviour including one asserting the dated row appears EXACTLY ONCE. Brief §3.4 rewritten from an open question to the shipped answer. Suite 1683 green, typecheck clean, quality gate passing.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 accepted the recommendation; the card was built and approved, so removing it needed his call.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7624,6 +7624,33 @@
         </is>
       </c>
       <c r="E176" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Plan · the target nest egg question — we may fill it in, but we say it is ours and let them change it</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Founder: 'we can enter target number but give them an opportunity to modify it. Add this verbiage to the question.' Written into brief §3.2. THIS CLOSES A LIVE HOLE: the shipped app has a row labelled 'Target nest egg' with a dollar figure the person never typed — the app works it out itself as the pot that reaches 80% odds. So we show someone a number, call it their target, and never mention we picked it. That is the founder's very first correction of this engagement, still live on the tab. THE FIX IS NOT AN EMPTY ROW: a blank target is a worse first experience than a sensible starting figure, since most people genuinely have no number in mind. So we fill it AND say whose it is, inside the question itself — 'What's your target nest egg? $1,250,000 — our starting figure, not yours. Change it to your own number.' For Pat the suggestion is $1,250,000, verified against the engine and pinned; note it sits well BELOW the $2,000,000 he actually typed, which is exactly the point — our suggestion and his ambition are different things and the screen must never blur them. THREE RULES: the row reads as ours until they touch it and as theirs the moment they do, with the qualifier disappearing once they type; changing it never moves the odds (the target is a yardstick, not an input); and it is never shown anywhere without the qualifier, because a suggestion that loses its label on one screen becomes a promise on that screen. Open question 3 in §10 is now answered and struck. THE GUARD CAUGHT MY THIRD MISTAKE OF THE DAY while pinning this: I solved the suggested target without the shared simulation inputs and got $70,000 instead of $1,250,000 — a silently wrong number I would not have spotted by reading.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; the app has been calling its own figure the user's target since before this engagement.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7653,6 +7653,33 @@
       <c r="E177" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Claude Design handoff v4 REVIEWED — all nine v3 blockers closed; five new items block a build</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Reviewed all 17 frames against brief v3-2026-08-14 and the v3 review. THE NINE BLOCKERS ARE CLOSED, and B1 was fixed the RIGHT way — structurally, with one arcPt(pct,r) formula driving every needle and fill arc instead of six corrected coordinates, which removes the defect class rather than the instances. Every figure I had pinned reconciles to the dollar: Pat's corrected accounts and 67% odds with range 20-98%, $77,500 landing at $2,008,196, the growth split, June's $985,000 and $8,155, Ray's 73-to-80 move, both state-6 cards, and the bad-odds frame. They also answered the brief's three questions back rather than guessing. FIVE NEW BLOCKERS, THREE OF THEM NUMBERS. V1: the below-yield mortgage frame draws '$380,000 at 3.1%' while printing the figures computed for the brief's $412,000 example — the yearly difference should be $5,814 not $6,304, and the lifetime figure $31,873 not $40,217; this is the frame the whole feature exists for, so it is the worst one to be wrong on. V2: the spend-more threshold buckets everything under $2,555 as 'about 9 out of 10', but the $500 stepper lands on $2,500 where the real answer is 81% — nine points, in the flattering direction, on the screen about spending more. V3: the mortgage caption is stated as fact again; review N3 established the simulation has no concept of debt so it charges that payment forever, and the previous note carried an explicit do-not-ship instruction that v4 dropped. V4: the DUE DEC 31 chip is 10.5px, below the 11px floor for a 55-to-70 audience. V5: amber now marks both 'you need to act' (Add rows) and 'this is our assumption, nothing is wrong' (ours chips) on the same day-one screen. Plus one prose-only slip: their note sums the growth split to $1,098,044 when it is $1,099,044 — the screen is right. AND ONE THING NOT THEIR FAULT: the target-nest-egg question must now carry the founder's 2026-08-14 ruling (suggest $1,250,000 and say it is ours and changeable); their note still lists it unresolved. V1 and V2 are pinned in the figures guard so a corrected file can be checked mechanically rather than re-read.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>The brief-figures guard caught both number defects; neither would have survived a re-read either, but the guard made it certain.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Claude (review of returned design)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7680,6 +7680,33 @@
       <c r="E178" t="inlineStr">
         <is>
           <t>Claude (review of returned design)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Plan redesign BUILT, then audited — 49 checks across calculations, features, flows and decisions</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Founder: build it, then audit 10 calculations, 10 features, 10 flows, 10 decisions. BUILT: the typed target end to end (store field, engine, a field to type it in, and our 80%-odds figure offered as a labelled suggestion while theirs is blank); the second dial; the closing sentence that projects rather than promises and explains that growth does almost half the work; three sub-tabs with Goals and Prepare landings; the mortgage-versus-Treasury comparison on Cash flow Debt in both directions; 'Can I spend more?' answering in place in plain English with every stepper position a live run; the Social Security claim row answering in place; and the dated obligation leading the decisions list. AUDITED, 49 CHECKS, and the audit was written to FIND things rather than to pass: calculations were re-derived independently rather than compared to the app's own helpers, features were rendered and driven rather than grepped, flows were walked end to end, and every decision was traced to shipped code rather than to a document. THREE REAL DEFECTS FOUND AND FIXED, all on day one — the first screen anyone sees. (1) Three of the seven questions were asked TWICE, because the work added a second component owning the same seven; that is the identical 'one question, one place' defect the founder found in Ray's hero, on another screen. (2) Retire-at and plan-to showed the app's own defaults with nothing saying they were ours — the same class as the target nest egg the app used to derive and label as theirs. (3) '$0' still printed for what counts and for big costs, which reads as 'you have nothing' rather than 'you haven't told us yet'; the brief named this and it was still shipping. One audit check failed for a NON-defect and is recorded as such: the dated withdrawal row was absent at age 72, which is correct because required withdrawals start at 73 — the audit setup was wrong, not the app. Workbook: docs/FCC-core-55-70/build-audit-plan-redesign-2026-08-14.xlsx. All four audits are committed as tests, so they re-run on every change rather than being a one-day exercise.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; an audit that only confirms what you believe is not an audit.</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7705,6 +7705,33 @@
         </is>
       </c>
       <c r="E179" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ENGINE — a loan payment can now END, savings can vary by year, and the mortgage odds are two real runs</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Founder: we tell the user we include the mortgage payment for the remaining duration — so we state it rather than asking. BUILT, all five pieces. (1) THE SIMULATION NOW KNOWS A PAYMENT STOPS. It charged a person's whole spending figure, inflated, for every year to the horizon — so anyone whose answer included a mortgage was charged it long after the house was paid off. Pat's clears in 2054 and his plan runs to 2058: four years of a payment that will not exist, making his odds pessimistic with no screen saying so. The payment is charged FLAT and never inflated, which is the reason it is a separate field rather than a spending adjustment: a fixed-rate mortgage is the same dollars in 2054 as today, and inflating it for 28 years would overstate it by more than half. (2) WHAT GOES IN CAN VARY BY YEAR, so paying extra is modelled as money not going into savings while the loan runs AND the whole payment freeing up once it clears — both halves, or it is an argument dressed as a calculation. (3) THE EXTRA PAYMENT PERSISTS; it was a text box that forgot the moment you left the screen, so nothing downstream could price it. (4) THE ODDS EFFECT IS TWO FULL RUNS, never a subtraction — the design's placeholder was 67 minus round(extra/500) times 2, a formula that will happily print a number no simulation produced. (5) THE CONSEQUENCE LINE NOW TRAVELS WITH THE CONTROL, which is the gap my own first build left: I moved the mortgage decision to the debt surface and left the retirement effect behind on Retire, exactly the risk the brief named as the whole reason to be careful about the move. TWO CORRECTIONS FOUND WHILE BUILDING: the payoff year rounded UP, putting a 338-month loan in 2055 when its last payment lands October 2054 — a year of a payment that does not exist, on the one figure a person checks against their own statement. And a contribution change dated after retirement does nothing, because there are no contributions then; a mortgage clearing at 79 stops draining savings rather than starting to top them up. Both now pinned. STILL TO DO before the caption can ship: the spending question must stop asking people to include debt payments, or we charge the mortgage twice.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; the caption could not ship while it described something the engine did not do.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7732,6 +7732,33 @@
         </is>
       </c>
       <c r="E180" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Spending question now EXCLUDES debt payments — the last piece, and the one that stops a double charge</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Founder: we tell the user we include the mortgage payment for the remaining duration. That settles who owns the loan — the app does, taken from the loan record itself, so the person never has to remember to include it. IT ALSO CREATES ONE RISK, AND THIS CLOSES IT. The spending question was prefilled from what a person spends now, and what they spend now INCLUDES their mortgage, because it is money leaving their account. With the engine now adding the loan on top, an answer given the old way would charge it twice — on Pat that is $2,400 a month counted double, pushing his odds well below the truth. So the question says what to leave out, at the point of answering: 'Not counting loan or mortgage payments — we add those ourselves, from your loans, for as long as they run.' And when a loan is on file it names it: 'We're including your $2,400/mo mortgage until it's paid off in 2054, from your loan.' The payoff year is computed from the loan's own arithmetic, not typed. THE DIVISION OF LABOUR IS NOW VISIBLE RATHER THAN SOMETHING A PERSON HAS TO WORK OUT, which is the same principle as labelling our assumptions 'ours' and the suggested target 'not yours'. All five pieces of the mortgage work are complete: the question, the engine's ending payment, the year-by-year contributions, the persisted extra payment, and the odds as two real runs. The caption the brief said could not ship is now true. Suite 1778 green, typecheck clean, quality gate passing.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; without this the honest engine would have produced a dishonest number.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7759,6 +7759,33 @@
         </is>
       </c>
       <c r="E181" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>BUILD 53 CUT — v1.1.0 #53, the Plan redesign and the mortgage engine work</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Founder said the literal 'cut the build' to the presented checklist, which is the only thing that counts under the release gate. GATES RE-RUN FRESH AT THE MOMENT OF THE CUT, not carried over from earlier in the session: clean working tree on taxonomy-v1.0.7 at 263f741, typecheck clean, 1796 tests green, quality gate passing, screen map regenerated with no new orphans. Last used iOS build number read off EAS as 52, so this is 53. WHAT SHIPS: the typed target nest egg end to end (the founder's first correction of this redesign, and until now the app derived a figure and labelled it as theirs); the second dial; the closing sentence that projects rather than promises and explains that growth does almost half the work; three sub-tabs with Goals and Prepare landings; the mortgage-versus-Treasury comparison in both directions with the retirement consequence attached as two real simulation runs; 'Can I spend more?' in plain English with every stepper position a live run; the Social Security claim row answering in place; day one showing all seven questions with our assumptions labelled as ours; and the engine change that lets a loan payment END — which raises the odds for anyone whose mortgage finishes inside their plan, a group whose odds have been pessimistic with no screen saying so. FOUR DEFECTS WERE FOUND AND FIXED BEFORE THE CUT by the two audits, three of them on day one — the first screen anyone sees. KNOWN AND GOING IN WITH IT: Claude Design still owes five corrections, so their drawing and the app will differ until that lands; what shipped uses the correct numbers, not the wrong ones in their file. NEXT: verify TestFlight arrival, then a device walk — the engine change is the thing to check, because it moves real numbers.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 explicit 'cut the build' to the pre-build checklist.</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7788,6 +7788,33 @@
       <c r="E182" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BUILD 53 FINISHED and SUBMITTED — verified on the build object, not from the log</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>v1.1.0 build 53, status FINISHED, read off the build record rather than trusted from CLI output: build id a75fe656-3e88-4fbf-8a51-bdb5b4ecf1c3, from commit 263f741, started 7:49pm and finished 7:55pm. Apple confirmed the upload — 'Submitted your app to Apple App Store Connect' — and it is now in Apple's processing, which usually takes five to ten minutes before it appears in TestFlight. NOTE FOR NEXT TIME: the auto-submit HELD this session. It has died with the session before (it is driven from the command line, so killing the session kills it) and had to be rescued with 'eas submit --latest'. That did not happen here; it completed inside the same run. THE DEVICE WALK SHOULD LEAD WITH THE ENGINE CHANGE, because it moves real numbers: a loan payment now stops when the loan does, so anyone whose mortgage finishes inside their plan will see HIGHER odds than before. Their odds have been pessimistic and nothing on screen said so. If the founder's odds jump and it feels wrong, that is the first thing to report. Also worth walking: the target nest egg is now his to type with our figure offered and labelled as ours; day one shows all seven questions with assumptions tagged; and the mortgage decision now lives on Cash flow · Debt with the Treasury comparison.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Verify status against the build object, never the log — the standing rule that caught a stale build number before.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Claude (verified)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7815,6 +7815,33 @@
       <c r="E183" t="inlineStr">
         <is>
           <t>Claude (verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Asset class renamed: "Stocks / ETFs" → "Stocks / Funds"</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "we should change ETFs to just Funds to include Mutual funds." ETFs are one kind of fund, and a person holding a Vanguard mutual fund was reading a label that did not name what they own. WHAT CHANGED: the class label everywhere it is shown — the net-worth grouping and its donut, the Performance composition bar, the add-account flow, the itemize picker, and the glossary card, which now reads 'funds — ETFs and mutual funds — that bundle many stocks together'. WHAT THE RENAME EXPOSED, and this matters more than the word: the label was HARDCODED IN EIGHT PLACES instead of read from the one canonical constant, and had already drifted into THREE forms — 'Stocks / ETFs', 'Stocks &amp; ETFs' and 'Stock / ETF' — all reachable in one session. That is the exact failure the calculation module exists to end. A guard now fails the build if any of the dead forms returns (src/__tests__/class_label_guard.test.ts), and it pins the exceptions so it cannot over-reach. WHAT DELIBERATELY DID NOT CHANGE: real product names ('Vanguard S&amp;P 500 ETF' is what that fund is called); the broker-coverage text, which accurately says an institution shares 'stocks, ETFs and mutual funds'; and the internal key `stocks_etf`, which sits in saved user data — renaming that is a migration, not a sweep, and carries risk with no user benefit. Approved mockups still show the old word and were left alone under the never-overwrite-a-mock rule; new mocks use the new label. 1921 tests green, typecheck clean.</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>Founder ruling 2026-08-17. A label that names only one kind of fund misdescribes what half the audience holds.</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-17)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7842,6 +7842,816 @@
       <c r="E184" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Income — all screens</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Income redesigned end to end: base pay as a full screen with one expandable section per earner (gross, 401(k), employer match, what lands); a 14-month dated pay table when pay varies; both earners captured, not one; a new filing-status question; bonus and stock follow the same who-earns pattern; interest and dividends calculated from holdings rather than asked, and treated as TAXABLE BUT NOT SPENDABLE.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>The app grossed up a typed take-home figure and taxed it back down, removing the 401(k) twice ($1,467/mo adrift). Nobody had ever set a filing status, so every couple was taxed as a single filer ($328–$866/mo). The household income was one person's against two people's spending. Dividends were counted as money you can spend when they are reinvested ($250/mo). Findings B27, B30–B35.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Income — mock</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>moneykeel_pres_mock_income-end-to-end_v02.html APPROVED. 14 screens in one document; 13 earlier income mocks archived.</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Mock-first standing order. One live version, the rest superseded not overwritten.</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Income — tax band, where it belongs</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>The tax band is produced ONCE, at total income (MK-CF-F-084 taxable annual → MK-CF-F-090 effective rate). The base-pay screen reads that band; it does not work one out. Both band lines in frame 2a call the same function with different income sets, and the screen says what it counted.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>A band is set by everything taxed together, not by a wage. The code already put it at total income; a second band inside base pay would have been two producers for one figure — the D2 fault we are removing. On base pay the band may be wages-only for now, so the screen states its base and re-reads it when other income is added.</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Income — interest and dividends</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Interest and dividends are WORKED OUT from the accounts (MK-NW-F-063 interest income annual), shown with the working, and correctable by the person. Whatever stands is taxed and is NEVER counted as spendable. The typed-only invAnnual path as the sole source is retired.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>The app holds the accounts, so asking invites a second, different answer to one question. Today invAnnual is counted as both taxed and spendable, inflating every surplus by about $250 a month — finding B34. Mock 3c.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Income — mock</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>income-v3-hifi-end-to-end-2026-08-27.html is the one live income mock. The onboarding frame and the "one component, two frames" rule were folded in from base-pay-v7 as frame 2e. Ten superseded income mocks moved to mockups/archive/.</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>income-v2 claimed the older mocks were archived (they were not) and that it superseded base-pay-v7 (it did not — v7 alone carried the onboarding frame). One latest complete version, as asked on 2026-08-27.</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Code — one name, one function</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Fifteen function names were each declared in two or more files; now none is. 560 functions, 560 distinct names. round2 stood in five files (one definition now, in the lowest layer); median, firstDate and onOrBefore were byte-identical copies; rmdDivisor and classifyHolding were adapters wearing the name of the function they wrapped (renamed rmdDivisorAtAge, assetClassForSymbol); daysBetween meant three different contracts (daysSince, daysBetweenDates, daysApart); num meant two (numOrZero, numOrNaN); a dead parseReceipt stub was deleted; MK-CF-F-005 actualMonthFlow was replaced by the This-month version and its only caller rewired. New guard src/__tests__/one_name_one_function.test.ts fails the build on any recurrence. 235 suites, 2,404 tests green.</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Founder ruling 2026-08-27: "fix it completely. No two functions doing same thing." The sweep that issues identifiers keeps whichever copy it walks first, so a second copy has no identifier, no master-file row and no header — invisible to every check while still running in the app. Two real defects fell out: the old monthsToClear loop capped at 1,200 months and reported a 100-year payoff for any longer loan, and actualMonthFlow dropped a logged debt payment whose debt had been deleted, raising the surplus by what had just been paid.</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Identifiers — orchestrators carry type O</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>An orchestrator is now MK-&lt;family&gt;-O-&lt;n&gt;, on its own counter per family: MK-CF-O-001 basePay, MK-CF-O-002 spending, MK-CF-O-003 thisMonth. The three F numbers they held (MK-CF-F-147, 154, 158) are retired with the reason and are never handed to anything else. 25 numbers are now retired.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Founder ruling 2026-08-27: "for orchestrator use O instead of F to make it easy to identify." An identifier is issued once and never re-pointed, so a type change means retiring the old number rather than editing it.</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Cash flow — build plan v03</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_spec_cash-flow-build-plan_v03.html: every row now carries its function and orchestrator identifiers and a status. Seven items done, three decided-not-built, one amend, four data changes, three parked. The duplicated "base-pay.ts amend" and "two earners" rows are merged — they were one job. v02 archived.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Founder request 2026-08-27: "update this file with function and orchestrator ID, and status."</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Code — two tax engines collapsed into one</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Deleted taxableIncome (MK-CF-F-093), marginalBracket (094), taxOwed (095), effectiveRateOnGross (096) and the pure alias estimateEffectiveTaxRate (047). Every caller now reads the filing-status-aware engine: taxableIncomeFor / marginalBracketFor / taxOwedFor / effectiveRateOnGrossFor. TaxProfile gained filing_status and over65 so the rows converted out of the onboarding profile are taxed by the same engine. STANDARD_DEDUCTION is now the single definition TAX_TABLES.single reads. grossFromNet inverts the surviving engine. Five identifiers retired.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>The app carried two complete tax engines, both live from the same profile on the same day — one of them unable to read a filing status at all. It reached the onboarding tax estimate, the Roth-vs-Traditional lean and the base-pay estimate. ZERO numbers moved: the two are identical arithmetic for a single filer (same bracket object, same $16,100 deduction) and nothing sets a filing status yet — every tax assertion still passes on its original expected value. It becomes correct for couples the moment the filing-status question lands.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Code — one take-home, and the employer match once</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Onboarding no longer defines takeHomeMonthly or employerMatchMonthly; both read the domain function. The inline third copy of the match rule on the employer-match step is gone. New guard src/__tests__/take_home_one_producer.test.tsx compares the two take-home paths across every persona. take_home_agreement.test.ts rewritten: it used to match the SOURCE TEXT of the local implementation, so it pinned the wrong arithmetic in place.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Onboarding taxed the full gross and took the 401(k) off afterwards; every other screen used the income grid, where a traditional contribution comes off BEFORE tax. $6,400 in onboarding against $6,560 everywhere else on the employedPartner persona — $160 a month, and only for a household with a partner. It is finding B05 again: B05 was fixed in the grid earlier the same day and never reached this copy. A second implementation cannot be fixed by fixing the first.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Code — the duplicate guard was too narrow, and a UTC date bug</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>one_name_one_function.test.ts now also reads src/screens, src/components, src/onboarding and app, and fails when a screen declares a name the calculation code already has. That found ten: employerMatchMonthly, takeHomeMonthly, currentAge, rmdStartAge, money, iso, pctTxt, prettyDate, clamp, volOf. All ten resolved — delegated where identical, renamed where the two answered different questions (signedMoney, pctToOneDp, weekdayDate, ageOrDefault). New MK-ST-F-065 isoLocalDate.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>MoneySheets and AccountDetailScreen stamped dates with toISOString() — UTC — while the cash-flow code used the local day, so an entry logged on the evening of the 31st west of UTC was filed in the next month, on those screens only. The name is now isoLocalDate so nobody reaches for the other one again. Lesson repeated from the orphan-route guard: a guard that looks in too few places is worse than none, because it reports clean and gets trusted.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Cash flow — months keyed by date (build step 1)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>New src/domain/income/salary-months.ts (MK-CF-F-163..170) with 9 laws. salaryByMonth is now a keyed table ('2026-07' -&gt; amount); an older twelve-slot array is still READ, as the calendar year the person is in now. salaryGrossByMonth, CashFlowScreen, IncomeSetupSheet and the onboarding month grid all go through it. A month the table does not mention falls back to the typical month, never to $0. 237 suites, 2,415 tests green.</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>A fourteen-month window running from last month crosses a year boundary, and slot 0 cannot mean both January and July. It also fixed a live defect: in the rolling frame a chip labelled JAN 27 wrote slot 0, which the domain read back as January of THIS year — the label said one year and the store meant another, and a slot carries no year to disagree with. Annual salary is unmoved on every persona (hourlyServer still $26,400).</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Cash flow — the partner's wage and two earners (build step 4, calculations)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>New src/domain/income/earners.ts (MK-CF-F-172..176, 8 laws): the partner's wage is its own block under the SAME field names as the person's own. MK-CF-F-060 salaryGrossByMonth now sums every earner, and employerMatchMonthly does too (MK-CF-F-177 wageGrossByMonth, MK-CF-F-178 wageMatchMonthly answer for one wage). MK-CF-O-001 basePay is the household orchestrator over a list of earners and shows the band on one wage and on all of them; MK-CF-F-171 earnerPay answers for one person. PlanHubScreen, CashFlowScreen and onboarding Summary now read the household. 239 suites, 2,427 tests green.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>The app asked 'Who earns this income? You / Partner / Both', stored the answer, and kept ONE salary — choosing 'Both' tagged a single wage as belonging to two people. Finding B32. Only MK-CF-F-060 changed: salaryAnnual sums it, MK-CF-F-084 reads that, MK-CF-F-090 reads THAT, so the band comes off both incomes with nothing above it touched. Three screens showed one person's wage as the household's — and the plan's income figure also only annualised monthly pay, so a fortnightly earner's plan was built on a fortnight.</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Code — today is the local day, not the UTC one</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Every 'today' stamp in src/ now uses MK-ST-F-065 isoLocalDate (or monthKey): 15 production files, 13 test files. New guard src/__tests__/local_day_not_utc.test.ts fails on any new call, with an allowlist for values that are genuinely UTC instants (a market bar timestamp, a provider sync cursor).</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>new Date().toISOString().slice(0,10) reads as today and is not — after about 5pm in California it already says tomorrow. An expense logged on the evening of the 31st was filed in the next month, a balance was stamped with a date the person had not reached, and a funded-this-month flag flipped a day early. It was in 35 places; only two were declared helpers the one-name guard could see, so the new guard checks the CALL rather than the name.</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Onboarding — the guided setup was unreachable (founder, build 53)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>routeGuard: a signed-in user on /onboarding now stays there in every state. It previously bounced to /(tabs)/home in three of four states. Two pinned assertions corrected, and a new guard walks every door on Home's first-run block (onboarding, connect, import, add-by-hand, monthly-income) in every state where Home renders, and fails if the guard bounces any of them.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>The founder on build 53: tapped 'Or answer guided setup questions', landed back on the same screen; tapped 'Pick up where you left off', landed back again — a circular loop with the entire guided setup behind it. FirstRunScreen sets onboardingComplete BEFORE Home is shown, and the guard treated /onboarding as a stray route for anyone complete — so the door was dead for every real user. Nothing in the guard routes anyone TO /onboarding, so 'not trapped' and 'not allowed' had been conflated into one line. Same class as T22.</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Cash flow — the tax band is on record (build step 6)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>MK-CF-M-029 'your tax band, on everything you are taxed on', produced by MK-CF-F-090 effectiveRate. New src/domain/income/tax-band.test.ts with 7 laws: the band reads every source not just the wage, a second wage counts, a partner means jointly until they say otherwise, jointly is never worse than single, 65+ never raises the bill and a couple can be two, one engine, and a typed rate always wins. 242 suites, 2,450 tests green.</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Steps 4 and 5 made the band correct; this proves it and records it. It had driven 25 functions since the app existed with no metric identifier — 163 metric rows were searched on 27 Aug and not one named it.</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Master file — metric identifiers come from a register, not a position</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>New moneykeel_metric_register.json (211 identifiers). nid() takes a key — family, the words on the screen, the underlying figure — and returns the number issued to it, wherever the row later moves. Seeded from the current build: all 223 metric and input identifiers verified unchanged. Proved by inserting a row at the top of the cash-flow list: zero identifiers moved, and the new row took the next free number.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>A metric's number was its POSITION in a list — nid() counted up as it walked them — so inserting a row silently renumbered every metric after it in that family. 93 audit findings are keyed to those numbers, as are the founder's typed answers: a finding would have reattached itself to a different figure with nothing to show it had. Same defect the function register fixed on 26 Aug, in the other half of the same file.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Standard — type list gains `master`; onboarding budget 37 → 38</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>moneykeel_naming_spec_file-and-folder-naming_v01.md: `master` added to the permitted types. flow_audit MAX_TOTAL_QUESTIONS 37 → 38 for the filing-status question; the REQUIRED ceiling is unmoved at 19.</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>The master workbook had no type that fitted, and naming it `schema` would have been a lie about what it is. The budget: filing status is pre-answered and skippable, so it adds a confirmation rather than a question. The founder's note on approving it was that onboarding still needs refining, so 38 is a holding position.</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Income — the tax rate is shown where the money is, and correctable</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Approved mock income-v4 (v03 archived), frames 2a and 2a-ii. MK-CF-O-001 basePay now returns takenOut {monthly, share, estimated, saysWhat, shortBy}. The base-pay screen shows what comes out; when it is our estimate it says 'federal income tax only', names the gap in MONEY (about 7.7% of a wage for Social Security and Medicare, plus any state), and offers the field. The onboarding Taxes step asks the SAME question in the SAME words. New rule 8c. 243 suites, 2,455 tests green.</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>The rate could only be changed on the Taxes step inside the guided questionnaire — itself unreachable until 28 August — and it asked for an 'effective tax rate % from last year's return'. That phrase means one thing on a return and another on a payslip: our figure is federal income tax only, about 12 points lower. A person could type 18 against our 9.2 and both be right, and their number drives every take-home figure in the app. FOUNDER RULING: the estimate STAYS federal. Payroll tax applies to wages, and our gross also carries rent, dividends and bonuses — applying 7.65% to that total would be wrong, not merely imprecise. State tax cannot be known without asking. So we work out the one thing we can, say so, and let it be corrected.</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Income — the federal bracket, the estimate, and one rate (mock income-v5 APPROVED)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>v05 approved; v04 archived. Base pay (2a-ii): 'Federal tax bracket' named, 'Estimated federal tax — assumes you take the standard deduction' in money not a percentage, the shortfall stated, then one field 'The tax rate you want us to use', with a line saying it drives every tax figure in the app. Summary (5a) is a RECAP: it shows the bracket and the tax at whichever rate is in force, says whose it is — 'your rate, 24% (edit on Your base pay screen)' — and asks nothing. New rules 8d (name the bracket, say what the estimate assumed, never 'effective tax rate') and a recap shows, it does not ask.</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Research: TurboTax divides total tax by AGI, the textbook definition by taxable income, others by total income — three products, three answers for one return, and TurboTax's own forums carry threads arguing it is wrong. So the phrase is a number a person cannot check. Planning tools (Fidelity, Empower) treat an effective rate as an assumption; paycheck tools (ADP, SmartAsset) never use the phrase and divide ALL withholding by gross. This is a paycheck screen, so it follows the paycheck convention and asks for a payslip figure.</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Income — what a typed tax rate does and does not drive (mock income-v5)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2a-ii: "We'll use 24% everywhere your take-home matters — cash flow, budget, what's left over. One-offs like a Roth conversion still use the tax tables." 5a: "Your 24%, used on every figure built from what lands in your bank." Replaces 'every tax figure in the app' and 'here and everywhere else'.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>A payslip figure is an AVERAGE rate. Four places need a MARGINAL one — the Roth conversion's tax bill, the Roth-vs-Traditional lean, capital-gains rates, and the tax drag in the retirement odds — because they ask what the NEXT dollar costs. Feeding an average into those is wrong invisibly: someone averaging 24% whose next dollar is taxed at 32% would be told a Roth conversion costs $2,400 when it costs $3,200, and advised to do it on that basis. The screen now promises only the half a payslip figure can answer.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Income — the tax rate built (mock income-v5)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>New src/domain/income/tax-rate.ts: MK-CF-F-181 rateInForce and MK-CF-F-180 enteredLandsAnnual, 8 laws. Three answers in order — TYPED off a payslip, IMPLIED by what they said lands in the bank, or OUR estimate — each carrying whose it is and what it covers. MK-CF-F-090 effectiveRate now returns it rather than deciding again. MK-CF-O-001 basePay returns tax {bracket, monthly, rate, whose, estimated, covers, shortBy}. The base-pay screen shows the named bracket, the estimated tax in MONEY, the shortfall, and one field. 244 suites, 2,464 green.</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Two gaps closed. A person could tell base pay exactly what lands and every other screen still estimated it — $572 a month apart on the founder's persona. Closing that exposed a second: a payslip rate is a share of GROSS and the income grid applied it to gross-minus-the-401(k), leaving $137. Both now zero across four wage shapes. A manual rate of 0% also turned out to be legitimate and was briefly being dropped.</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Cash flow — dividends out of take-home (build step 7, finding B34)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>extraIncome gains reinvestedMonthly; the income grid subtracts it from what lands. New profile field invPaidToBank ('no' by default = reinvested). The onboarding dividends screen now asks 'Does this reach your bank?' and says what the answer means. New src/domain/income/dividends.test.ts, 6 laws. 245 suites, 2,470 green.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Interest and dividends were counted as money to spend. In most accounts they are reinvested where they are earned and never reach the bank, so every surplus, runway and savings figure was too generous by the whole dividend — $250 a month on $3,000 a year. The correction is NOT simply removing them: they are still taxed, so the tax still comes out of the pay that does reach the bank. Someone with $3,000 reinvested now lands $5,517 a month against $5,572 with no dividends at all — $55 less, which is the tax on money they never see. A simple removal would have shown them $5,572 and been wrong in the other direction.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Cash flow — dividends worked out from the accounts (build step 8)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>New MK-CF-F-184 incomeFromAccounts (7 laws) with MK-CF-F-183 paidOutByAccount: one line per account showing the working, matching the approved mock ($699 Chase, $1,260 Treasuries). The onboarding dividends screen shows it with a Use button. Accounts we cannot read are NAMED, not assumed to pay nothing.</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Three screens computed investmentIncomeAnnual(transactions) + interestIncomeAnnual(accounts) — the coupons actually received PLUS the coupons those same bonds are expected to pay. A $10,000 Treasury at 5% that had paid its $500 showed as $1,000 of income, on the Tax organizer, Income detail and Income manager. One answer per account now. Two things it cannot do: no holding carries a dividend yield, and assetClassOf answers 'mixed' for a brokerage, an IRA and a 401(k) — so a check for 'stocks_etf' saw none of them and the first version claimed to have covered everything.</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Cash flow — the gross-up branch deleted (build step 2)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>salaryGrossByMonth no longer inverts the tax schedule. New take-home-mode-migration.ts (MK-CF-F-185/186, 6 laws) converts salaryMode:'takehome' ONCE, on the way into the store: what they typed becomes landsTypical, the gross is worked back and stored, the mode becomes 'gross'. grossFromNet now has exactly one caller — that conversion.</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>The branch inverted the tax schedule on EVERY READ to find a gross that would produce a typed take-home — a guess laid on an estimate. It could not simply be deleted: stored profiles still carry the mode, and reading that number as gross would overstate someone's income by their whole tax bill.</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Cash flow — Your income, all of it (mock income-v5, 5a and 5b)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>New MK-CF-O-004 incomeSummary and src/screens/IncomeSummaryScreen.tsx, route /income-summary, reached from the Cash flow Income tab. Two totals: what lands each month (per earner, plus rent) and what the year is taxed on (per source). It SHOWS the bracket and the tax at whichever rate is in force and says whose — it never asks. A fresh account keeps both headings and shows no invented $0. 6 tests.</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>A recap shows, it does not ask: the rate is set on Your base pay and every other screen reads it. And two totals, never one — mixing them is how a take-home figure comes to include a bonus nobody has been paid.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Onboarding — the base-pay step IS the base-pay screen</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>income_salary now renders BasePayScreen with frame='onboarding'. The component writes as it goes rather than on a Save the host never presses, and the host keeps its own progress bar and Continue. income_401k and employerContribution are no longer separate steps when there is a job — the screen carries both inside each earner's section. They REMAIN for a retirement planner with no employment income. 248 suites, 2,492 green.</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>One component, two frames (mock rule 2b). Onboarding had its own copy of the base-pay questions — one earner, its own wording — while Cash flow opened a different screen with a section per earner; four places could set a salary, now two. The 401(k) had to stay conditional: contributionsByType asks for Roth, taxable and property but NOT the 401(k), so dropping the steps outright would have left a jobless retirement planner unable to enter a contribution anywhere.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Onboarding — a 401(k) is asked only where one can legally exist</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>The 401(k) and employer-match steps now appear ONLY for someone self-employed without a wage — a solo 401(k), with no base-pay screen to hold it. A wage brings the base-pay screen, which carries both. No earned income at all means the question is not asked. Four laws in flow_audit cover wage / self-employment only / no earned income / both.</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Founder challenge: 'If someone is not working, how can they contribute to 401K?' They cannot. The IRS rule is that contributions come out of COMPENSATION — wages, or self-employment earnings. A pension, Social Security, rent or dividends earn nobody the right to contribute, so the version shipped an hour earlier asked a question whose only valid answer was zero. It was also wrong the other way: keyed on 'employment' alone, it denied the screen to a self-employed person with a real solo 401(k).</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Tests — a fixture that asserted freshness had a fixed date</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>invest_fcc.test.tsx: the bond's value_as_of was pinned to 2026-03-03 and asserted to be FRESH. It aged past the six-month staleness line on 1 September and the test failed on the calendar, not on the code. Both fixture dates are now relative to today.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Caught while running the suite after an unrelated change; confirmed by stashing the change and seeing it fail anyway. A test that asserts a value is fresh cannot hold that value's date still.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Every statutory constant checked against its published source — three errors found</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>New src/__tests__/statutory_constants.test.ts: the 2026 bracket tables and deductions, the complete IRS Uniform Lifetime Table (72–120, typed in whole; the interpolation fallback deleted), the SECURE 2.0 start ages, and the SSA claim factors (70% at 62, 124% at 70, FRA 67) — all typed in from the published figures, never from our own constants. IRS_LIMITS corrected: IRA 7,000→7,500, catch-up 1,000→1,100 (the 2025 figures had been carried forward). annual401kLimit now knows the 60–63 super catch-up of 11,250. 249 suites, 2,499 tests green.</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>The founder asked how he can trust the formulas given how many errors his reviews find. The honest answer: stop checking the code against itself. First run against the world found the IRA limits a year stale, the 60–63 super catch-up absent — in an app built for ages 55–70 — and four RMD divisors reading 0.1 low because the table skipped ages and interpolated: a $925 understatement of a legally required withdrawal on $500,000 at age 98.</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>JJ</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8652,6 +8652,195 @@
       <c r="E214" t="inlineStr">
         <is>
           <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Standard — an `audit` folder and type</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/ created with its README; sub-folder list gains `audit` (7th), type list gains `audit`. The build-54 device-test sheet moved there as moneykeel_build_audit_device-test-build-54_v01.xlsx.</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Founder ruling: checking the work is its own kind of paper. It had been filed first in the old docs/ folder by habit, then under standards/ where rule 5 forces anything typed `spec` — neither is where a verification record belongs, and neither would let anyone find what was checked against a given build.</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Base pay — the founder's build-54 device findings, all nine (mock income-v6)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Mock v6 approved and live (v5 archived): one bracket row with the assumed-jointly subline; the estimating card ADDS UP (gross − tax − 401(k)s = lands, with a 401(k)s row); a NEW mixed frame 2a-iii — entered figures read back, estimates named to their person with dollars, no single tax row; monthly everything-else from the function; copy and ≈ fixes. Code: estRate injected by MK-CF-O-001 so every estimate uses the ONE household rate; whoEarns implies jointly (stated); landsNote/mode/monthly401k on the orchestrator. 4 new laws; 249 suites, 2,503 tests green. Feedback workbook: audit/moneykeel_build_audit_device-test-build-54-feedback_v01.xlsx.</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Nine findings from the founder's first device pass, two accuracy-class: the card contradicted itself ($21,159 − $4,380 − $1,656 ≠ $16,403 — every estimated earner was granted the FULL joint deduction), and a two-earner household was banded as single (32% vs jointly 24%) because 'Both of us' set nothing the filing default could see.</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Base pay (2a)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Mixed-household take-home note is now a labelled fact per person: “Your take-home: $5,000 (you entered) · Sam’s take-home: ≈$3,686 (calculated — gross less federal tax and 401(k))”. No prose.</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Founder wording. The prose version (“worked out”) was misread — the entered $5,000 was taken for gross.</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Every income screen + mock v06</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>One term per concept: “take-home” (retired: lands in your bank, takes home) and “calculated” (retired: worked out, Estimated federal tax, our estimate) — base pay, income summary, filing status, plan hub, contribution room, income-end-to-end mock. Guard test one_term_per_concept.test.ts enforces it.</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Founder order: “Always use same words to describe same thing in the app. There is no score for creative writing.” Two words for one thing read as two different numbers.</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>App-wide</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>“One term per concept” made an app-wide standing order: written into CLAUDE.md and the taxonomy spec (canon table with retired words); guard widened from the income screens to ALL of src/ + MoneyKeel/functions. The wider net caught 18 more — glossary title “How we work out your odds”→“How we calculate your odds”, onboarding “Use our estimate”→“Use the calculated rate”, dividends “It lands in your bank”→“It is paid into your bank”, plus comments.</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Founder order 2026-09-02: make one-term-per-concept a rule across the app.</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Plan hub · Retirement cockpit</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Simulation count corrected on screen: "~400 market simulations" → "1,000" in 4 places. The engine has run 1,000 paths since the B6 precision fix; the screens were never updated. Guard now bans "~400".</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Wrong number reaching a screen — found by the app-wide synonym sweep.</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>JJ (rule); fix per accuracy standing order</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>App-wide</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Synonym sweep findings: canon stragglers fixed under the existing take-home/calculated rule (work-it-out, estimated-from, what-lands variants — 5 new guard patterns); 16 further synonym clusters compiled for founder ruling in moneykeel_audit_decisions_synonym-clusters_v01.xlsx (audit folder). No cluster renamed without a ruling.</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>One-term-per-concept rollout.</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>pending JJ rulings</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8841,6 +8841,384 @@
       <c r="E221" t="inlineStr">
         <is>
           <t>pending JJ rulings</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Home · Onboarding flow</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>The connect door reads "Connect your bank ›" on Home, which still said "Connect your first account ›"; Home now takes it from the one list of doors. Onboarding spec v02.</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Founder ruling on his build-53 onboarding note.</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Home · Sharpen your plan · Plan (What counts toward retirement) · Add account</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>"Add something by hand ›" opens the Add account form in one tap on all three screens, with the same line under it: "Your home, savings, or an account with no login." Home used to open the Net worth tab, four taps from the form. The first account saved by hand also creates the rows for accounts named during setup, which only the Net worth tab did before. Onboarding spec v03.</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Founder: "love it. do it." — one destination, one wording, nothing lost from setup.</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>App-wide · the ways to add an account</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>One door, one term: 'Link it (read-only)', 'Add by hand', 'Import from a file' on every screen that offers them, under the heading 'How do you want to add an account?'. Replaces 'Connect your bank ›' / 'Import a file from your brokerage ›' / 'Add something by hand ›' and Net worth's first-day 'Connect a brokerage' / 'Add a file from your bank' / 'Type it yourself'. Mock first: moneykeel_pres_mock_ways-to-add-an-account_v01.html.</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Founder: 'one door one term rule - so change on all.'</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>App-wide · type</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Every screen title is 20 points. Today 31 screens use 24, Cash flow 30, Will it last and Look back 20.</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Founder: 'standard size 20'</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>App-wide · titles</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>A screen does not need a title; the Net worth tab keeps none. Withdraws the same day's 'we cannot have screen without title'.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Founder: 'I take back title not need for every screen.'</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>App-wide · top bar</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>MoneyKeel at the top of every screen, not only the tab screens. Drawn in the ways-to-add-an-account mock v10 for approval before it is built.</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Founder, reviewing mock v09 of the import screen</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>JJ (direction; mock to approve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Net worth mock v06 CONFIRMED as the approved Net worth screen: the screen as Build 53 shipped it — square, edge-to-edge dark-green and light-green bars, the odds leading the retirement line, source chips on account rows, the bar following the By institution toggle, one-hue debt bar, Reconnect beside Sync now. MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_net-worth-quiet-instrument_v06.html</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Mock v5 was the last Net worth mock; the square corners and other changes were built 2026-08-11 to 08-14 without one, so no picture matched what shipped</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "This is the right one."</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>App-wide</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Odds — exact, no rounding — Supersedes Brief B6 (2026-08-20) and C2 (2026-09-08), which both said nearest 5. Drawn in Net worth mock v08; the app and the file change together once v08 is approved.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "per the latest ruling use exact everywhere no rounding for odds"</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Return on cash + investments — two decimals — The precision standard (Q49) already says two decimals for returns; the master row and the app said one. Drawn in v08.</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "Return on cash - use 2 decimals"</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tight ⚠ beside the emergency fund — kept — A named exception to Brief R3 (show the fact, not the verdict).</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "tight besides emergency funds - keep it"</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>App-wide</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Source chip — Linked, date only when stale — Applies Brief R7 (source always, date only when stale) to the chip.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "connected only unless stale"</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>App-wide</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Linked / Link again — One term per concept: the door says 'Link it (read-only)', so an account that went through it is 'Linked' and the repair is 'Link again'. A canon row is added when it is built.</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "connected / reconnected - change to linked / link again"</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Headings — dark bars and light-green bars — Said about Net worth's five bars. Open: whether it also replaces the quiet section labels on the Plan tab (2026-08-13 rule).</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "full green bars - dark bars for section headings and light green for sub-headings"</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Net worth first day — no duplicated doors — Drawn in v08: one line and one set of doors under What you own; the same fix applied to Debts.</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Founder review of Net worth mock v07</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "State C - what you own section has 'add account three times, + how you want to add an account - too much duplication"</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9219,6 +9219,33 @@
       <c r="E235" t="inlineStr">
         <is>
           <t>Founder (chat 2026-09-14): "State C - what you own section has 'add account three times, + how you want to add an account - too much duplication"</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Net worth mock v08 APPROVED and built: the three ways to add an account once on the first day (one line, no repeated 'Add your accounts ›', no separate heading), the add sheet titled 'How do you want to add an account?', '＋ Add an account', the hero line opening the sheet, the return to two decimals, 'Linked' with a date only when stale, 'Link again' on the fix sheet and everywhere a link is repaired, and the odds exact everywhere. MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_net-worth-quiet-instrument_v08.html</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>The founder's rulings on v07 and the one door, one term ruling</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "approved. code, test, commit."</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E236"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9246,6 +9246,276 @@
       <c r="E236" t="inlineStr">
         <is>
           <t>Founder (chat 2026-09-14): "approved. code, test, commit."</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Performance FINAL (2026-08-04) CONFIRMED as the design to work with — MoneyKeel/documents/networth-and-performance/archive/2026-08-10_moneykeel_pres_mock_performance_v01.html (identical to the Claude Design handoff of 2026-08-11). Build 53 did not match it: the older Invest sections stayed below it, the Since chip crashed, the walks back-solved to negative beginnings, the home got its own walk, and the account page lacked its walk, per-holding returns and Total.</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Performance step (start from the last approved design)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-14): "performance final is the one to work with"</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Mock v11 drawn from v10 with the founder’s four changes: (10) the window chips sit on ONE row in 10.5-point type with the app’s 12-point corner radius instead of semicircle ends — measured at 355 of the 362 points a 390-point phone gives; (11) the summary graph gets a Y AXIS with dollar gridlines, and its line now starts at the window’s beginning value and ends at its ending value; (12) the account header reads Market value · Wealth generated · Return — the same three figures, order and words as every other screen, with income staying in the walk and under each holding; (13) day one for a LINKED account should not be zeros — rebuild the line from the broker’s own transaction history priced at each day’s close (founder decision pending).</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Founder review of Performance v10, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-25) — v11 SENT FOR APPROVAL; mark 13 is his decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TWO DEFECTS FOUND answering his questions. (a) The account header Return is worked out from cost since purchase ((balance − cost) ÷ cost) while the walk beneath it uses the window (wealth generated ÷ beginning) — two different returns on one screen; and the header’s third figure, Income $220 (dividends + interest), never reconciled with the +0.57% that comes from wealth generated $300. (b) portfolioTrend values TODAY’s share count at past closing prices, so the graph shows a line that never happened and cannot match the broker’s statement — against the screen’s own promise, “We never back-fill a year we didn’t see.”</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Founder questions on the E*TRADE account screen and day-one history, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Claude — recorded in the workplan; both fixed by v11 marks 12 and 13 once approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>App-wide · selectors</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Selector corner radius counted app-wide: 23 places use the semicircle (Radii.pill) and 157 use the 12-point corner (Radii.md). The Performance window chips were semicircles and are corrected in v11. The remaining semicircle selectors (Monthly income, Net worth group pills, Bonds, Income manager, SnapTrade connect, Job safety and others) are a workplan row, screen by screen with its own mock.</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: “make the buttons same as all radio buttons across all screens — rounded corners not semicircle ends”</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Founder (direction) — Performance done in v11 mark 10; the sweep is TO DO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mock v12. (a) CHIP SHAPE FIXED PROPERLY: the radius was already 12, but the chip was 26 points tall — any radius at or above half the height draws a semicircle, which is why they still looked round. Chips are now 42 points tall (the height the app’s other radio buttons use) with the same 12-point radius. (b) THE RETURNS COME OFF THE CHIPS: measured, five chips carrying returns need 434-492 points against the 362 a 390-point phone gives — they only fitted before because four windows had no data; a chip now carries its window only (labels 305-348 points) and the return is read from the summary beneath. (c) DAY ONE REBUILT, APPROVED: a linked account’s history is rebuilt from the broker’s own transactions priced at each day’s close, starting at the broker’s first record, with the source named on screen; hand-entered accounts and cash start the day they are entered and say so.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Founder review of v11, 2026-09-25: "Yes rebuild - day one history" and "buttons are still not square with rounded corners"</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-09-25) — rebuild APPROVED; v12 sent for approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TWO MORE DISAGREEMENTS FOUND in today’s code while drawing v12. (a) The summary Return counts price change only, weighted across holdings, while “Wealth generated” next to it counts dividends and interest too — on the final design’s example they agree by luck (+0.54% ≈ 1,910 ÷ 352,404), on real data they will not. The build uses one meaning: wealth generated ÷ the money working in the window. (b) A 2Y return is annualised (ruling 2026-08-18) while every other window is a window rate, and nothing on the screen says so; the summary will say “a yearly rate” when 2Y is picked.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Drawing Performance v12, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Claude — both recorded in the workplan and fixed by the v12 build</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mock v13. THE WINDOW SELECTOR IS ONE CONTROL: a single bordered row split by hairline dividers, five equal segments of 71 points filling the card’s 362, each 42 points tall, the chosen one wearing the light-green fill and dark-green bold type every other radio button in the app uses when chosen. Each segment carries its window only (Since · 1M · This year · 1Y · 2Y); the window’s start date and its return are read from the summary band directly below. Five separate buttons — even at the right height and radius — never read as one thing.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: "button still looks not asthetically good. Can it be done like one row with dividers for different periods?"</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Founder (direction) — v13 sent for approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Day one for a HAND-ENTERED account wrongly showed the “Linked” chip on each account walk. It now carries the app’s own hand-entered wording from SourceChip — “✍️ By hand · you update it”. Linked accounts never appear on that phone: since the rebuild was approved, a linked account gets its history rebuilt and has its own phone.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: "why the accounts say linked if hand entered?"</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Founder (finding) — corrected in v13</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mock v14 — the window selector, designed. A quiet tray (#EEEEE9, 12-point radius, 3-point inset) holds five segments; the chosen window is lifted onto a white card with a soft shadow and dark-green type, the resting windows are separated by hairline dividers inset from the edges (the dividers beside the chosen card are hidden). Every segment carries TWO lines: the window with its date above (11 points), its own return beneath (13 points, tabular figures); a window with no records shows “—” in light grey. The Since segment is 1.55× the width of the others because it carries a date. Measured: 97 + 66 × 4 = the card’s full 362 points, 52 points tall, nothing clipped. Also added: “2Y is shown per year, so it sits fairly beside 1Y” under the selector wherever a 2Y figure shows.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: "cannot see since when? and what %? may be make it two rows, one for time period and second for return below it." then "Design as UI designer"</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Founder (direction) — v14 sent for approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>MOCK v14 APPROVED AND BUILT ("approved. save and built it"). The screen is now the approved design and nothing else: the window selector (one control, five windows, two lines each), the summary with a Y-axis value line drawn only from days the record holds, the all-accounts walk, one walk per INVESTMENT account titled by account, and what each category earned. ONE MEANING OF RETURN everywhere on it — wealth generated ÷ the money working in the window; a window with nothing behind it shows —, never +0.00%. DAY ONE IS REBUILT for a linked account from its own transactions priced at each day’s close, and the screen names the source and the first day; hand-entered accounts and cash say they start the day they were entered. REMOVED, not in the design: Your return, Honest comparison, Winners &amp; laggards, Look ahead / Look back, Your investments, Add investment / Import / Record / Activity. New: Calculation Module code/engines/rebuild-history.ts, store.rebuildLinkedHistory, closeOnOrBefore. Tests: 2,832 green including 14 for the rebuild engine, 4 for the store pass and 13 for the screen.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Founder approval of mock v14, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-09-25; built the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9516,6 +9516,33 @@
       <c r="E246" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-09-25; built the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Performance · standards</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>A RETURN OVER A WINDOW LONGER THAN A YEAR IS A YEARLY RATE, AND SAYS SO. The segment carries the yearly rate with “a year” under it, and the summary states both: “+15.10% over the two years, which is +7.30% a year.” A window of a year or less is never annualised. Checked before it was written: GIPS forbids annualising under a year and annualises above it, brokerage statements match, and Fidelity’s help warns that cumulative returns of different lengths must not be compared. Written into MoneyKeel/documents/standards/moneykeel_calc_spec_precision-and-display_v01.md § A return over a window longer than one year, and into the rulings ledger.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-25: "2Y - should not be annualized … double check what financial insititutions do." then "Your recommendation approved. Add it to standards."</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-09-25; built and written into the standard the same day</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9543,6 +9543,87 @@
       <c r="E247" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-09-25; built and written into the standard the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>THE EIGHT OPEN QUESTIONS ON PLAN ARE SETTLED (founder: “Plan - Q1 - 8 - your recommendation approved”) and drawn in mock v06: (Q1) extra saving is the eighth glance row; (Q2) the facts save as you type; (Q3) past target the dial caps at 100% with the numeral reading the true 114%; (Q4) day one offers our target and says whose it is; (Q5) the mortgage row states today’s odds and stops until a second full simulation exists; (Q6) the retirement sentence is in today’s money, after tax, and says so; (Q7) one odds number everywhere — a code fix in the build; (Q8) Ray stops treating 80% as a line he crosses. THE FIVE BLOCKERS ARE FIXED: the below-yield mortgage frame recomputed for its own balance ($5,814/year, $31,873 over the life), the spend-more buckets corrected (under $2,200 is 90 out of 100; above it 80 out of 100; $2,480 is the most she can spend holding 80), the mortgage caption made honest, the 10.5-point chip raised to 11, and “ours” given a neutral chip so amber means only “needs you”.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-26</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED (the recommendations); drawn in v06 the same day</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Plan · figures</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>EVERY PLAN FIGURE RE-RUN AT 1,000 FUTURES, the count the app itself runs — the brief’s 400-run numbers are superseded: Pat 67% → 66.4%; his projection $2,008,000 → $2,006,000; the gap closes as $542,500 saved + $554,692 growth; the pot that reaches 80% odds $1,250,000 → $1,400,000; June’s draw $4,155 → $4,080 and her paycheck $8,155 → $8,080; her room to spend more $2,555 → $2,480; Ray 73%/80% → 70.4%/78.9%. The mock also stopped being a template: every placeholder is filled with the figure the function gives, and every dial needle with the design’s own formula, so the file reads on its own.</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>The Plan screen step, 2026-09-26</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Claude — computed, not carried over</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>App-wide · words and precision</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>THE CANON GUARD READS COPY AS IT RENDERS. It scanned the syntax tree, so a canon entry written with punctuation (row 14’s “} a year”) could never match — it reported the app clean while Performance printed “{pct(perYear)} a year”. It now also reads JSX children joined with their expression boundaries and templates reduced to head + “}” + literals; identifiers inside expressions cannot raise a false alarm and spoken labels stay exempt. Turning it on found 26 real violations across 14 files — all fixed, a figure now carrying /month or /year. PRECISION: the founder’s ruling on the sentence — “+7.30%/year”, canon-literal. Net worth’s debt APR and Home’s hero return moved to two decimals; the cushion keeps one decimal and says why; the 48 remaining one-decimal percentages are held by a new ratchet.</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-26: “go with (a) … fix canon guard … fix decimel error on NW screens”</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Founder (direction) — all built and tested the same day (commit 5d262d6)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9624,6 +9624,33 @@
       <c r="E250" t="inlineStr">
         <is>
           <t>Founder (direction) — all built and tested the same day (commit 5d262d6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>App-wide · rulings</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>THE TAX STANCE IS NOW IN A STANDARD, not only on the master’s rulings tab. G6 (2026-09-08) and G7 (2026-09-12) — no built-in tax rates, the person’s own rate or no number with the reason — were in the master and in no standard, on no screen row, while the workplan carried a row of mine recommending the opposite. So a screen task that read the standards and the tracker could not see them, and I re-asked a settled question. Written into the precision-and-display spec (§ What a money figure means — before or after tax), with what a screen may never print. New lookup: Calculation Module code/scripts/rulings-for.py &lt;topic&gt; prints every ruling that mentions a subject, in his words, and CLAUDE.md now says to run it before writing copy on a ruled subject.</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Founder, 2026-09-26: “how did you miss my earlier rulings” / “where they not in the master file or standards documents?”</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Claude — the gap he found, closed</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-08-14.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9651,6 +9651,33 @@
       <c r="E251" t="inlineStr">
         <is>
           <t>Claude — the gap he found, closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Cash flow · income</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Income end to end v07 (v06 archived the same day) — the row this file never got until 2026-09-26, when the founder asked what changed between them. THE FIGURE: the estimating card’s household row read ≈$10,442/month while the take-home line under it read ≈$9,242 — one card disagreeing with itself; corrected to ≈$9,242. THE CAVEAT: the federal-only line now names the gap in MONEY (“the take-home above is higher than it will really be, by roughly $880 a month”) instead of only a percentage. THE WORDS: the canon applied throughout — one-off → one-time, /yr and /mo → /year and /month, “what you told us” → “what you entered”, “we work out” → “we calculate”, “what’s left over” → “the surplus”. Nothing else moved.</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-09-26: a version existed with no record of what changed</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Claude — recorded late, and the rule that prevents it is now in the naming standard</t>
         </is>
       </c>
     </row>
